--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -800,12 +800,7 @@
         <v>114024893</v>
       </c>
       <c r="B3" t="n">
-        <v>5164</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,7 +838,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 55708-2023 (A 55708-2023), Vg</t>
+          <t>A 55708-2023, A 55708-2023, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>114024893</v>
       </c>
       <c r="B3" t="n">
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,254 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129948805</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stora Dammtjärnen, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>339997</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6395887</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Minst 2 ex.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129948435</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58106</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Dammtjärnen, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>339955</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6395725</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Härryda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 3 ex. Skiktad barrskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>129948805</v>
       </c>
       <c r="B4" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129948435</v>
       </c>
       <c r="B5" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>129948805</v>
       </c>
       <c r="B4" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129948435</v>
       </c>
       <c r="B5" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>129948805</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129948435</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>129948805</v>
       </c>
       <c r="B4" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129948435</v>
       </c>
       <c r="B5" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>129948805</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>58113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>129948435</v>
       </c>
       <c r="B5" t="n">
-        <v>58198</v>
+        <v>58113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114024711</v>
+        <v>114024893</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,47 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>102204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 55708-2023, Vg</t>
+          <t>A 55708-2023, A 55708-2023, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339891</v>
+        <v>340018</v>
       </c>
       <c r="R2" t="n">
-        <v>6395947</v>
+        <v>6395732</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,58 +792,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114024893</v>
+        <v>129948435</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102204</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 55708-2023, A 55708-2023, Vg</t>
+          <t>Stora Dammtjärnen, öster om, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>340018</v>
+        <v>339955</v>
       </c>
       <c r="R3" t="n">
-        <v>6395732</v>
+        <v>6395725</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +869,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 3 ex. Skiktad barrskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +904,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -917,7 +919,7 @@
         <v>129948805</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,32 +1040,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129948435</v>
+        <v>114024711</v>
       </c>
       <c r="B5" t="n">
-        <v>58198</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1072,23 +1074,21 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Dammtjärnen, öster om, Vg</t>
+          <t>A 55708-2023, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>339955</v>
+        <v>339891</v>
       </c>
       <c r="R5" t="n">
-        <v>6395725</v>
+        <v>6395947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,27 +1115,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 3 ex. Skiktad barrskog.</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,12 +1145,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 55708-2023 artfynd.xlsx
+++ b/artfynd/A 55708-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114024893</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129948435</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129948805</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1154,8 +1174,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114024711</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>